--- a/static/downloads/Neverlank_FX_Rates_Import_Template.xlsx
+++ b/static/downloads/Neverlank_FX_Rates_Import_Template.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F2942"/>
+        <bgColor rgb="000F2942"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,10 +63,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +431,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -436,22 +443,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Rate (ZWG per 1 USD)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -487,9 +494,17 @@
           <t>RBZ auction</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8Neverlank Chartered Accountants&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>